--- a/r4-core-148-apply-template-for-base-igs/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-148-apply-template-for-base-igs/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="428">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T17:40:42+00:00</t>
+    <t>2026-10-20T06:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -712,6 +712,12 @@
     <t>GDA-OID</t>
   </si>
   <si>
+    <t>Gesundheitsdiensteanbieter-OID (GDA-OID)</t>
+  </si>
+  <si>
+    <t>The OID of the healthcare service provider (Gesundheitsdiensteanbieter, GDA) as registered in the Austrian GDA-Index. The OID is assigned by the Federal Ministry of Health (Bundesministerium für Gesundheit).</t>
+  </si>
+  <si>
     <t>Practitioner.identifier:GDA-OID.id</t>
   </si>
   <si>
@@ -733,7 +739,7 @@
     <t>Practitioner.identifier:GDA-OID.system</t>
   </si>
   <si>
-    <t>A GDA in Austria is represented via an URI (OID)</t>
+    <t>A Gesundheitsdiensteanbieter (GDA) in Austria is represented via a URI (OID)</t>
   </si>
   <si>
     <t>urn:ietf:rfc:3986</t>
@@ -742,7 +748,7 @@
     <t>Practitioner.identifier:GDA-OID.value</t>
   </si>
   <si>
-    <t>OID for the GDA in Austria</t>
+    <t>OID for the Gesundheitsdiensteanbieter (GDA) in Austria</t>
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.period</t>
@@ -861,6 +867,12 @@
     <t>VPNR</t>
   </si>
   <si>
+    <t>Vertragspartnernummer (VPNR)</t>
+  </si>
+  <si>
+    <t>The contract partner number (Vertragspartnernummer, VPNR) of the practitioner, assigned by the Federation of Austrian Social Insurances (Dachverband der österreichischen Sozialversicherungsträger).</t>
+  </si>
+  <si>
     <t>Practitioner.identifier:VPNR.id</t>
   </si>
   <si>
@@ -918,6 +930,12 @@
     <t>vbPK</t>
   </si>
   <si>
+    <t>Verschlüsseltes bereichsspezifisches Personenkennzeichen (vbPK)</t>
+  </si>
+  <si>
+    <t>The encrypted sector-specific personal identifier (Verschlüsseltes bereichsspezifisches Personenkennzeichen, vbPK) of the practitioner, used in Austrian e-Government processes. The OID of the system identifies the sector (e.g. GH for Gesundheit, SV for Sozialversicherung, AS for Amtliche Statistik) according to the E-Government-Bereichsabgrenzungsverordnung (E-Gov-BerAbgrV).</t>
+  </si>
+  <si>
     <t>Practitioner.identifier:vbPK.id</t>
   </si>
   <si>
@@ -933,7 +951,7 @@
     <t>Practitioner.identifier:vbPK.system</t>
   </si>
   <si>
-    <t>OID for the specific vbPK in Austria</t>
+    <t>OID for the specific verschlüsseltes bereichsspezifisches Personenkennzeichen (vbPK) in Austria</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/core/r4/ValueSet/at-core-vbpk</t>
@@ -1128,11 +1146,10 @@
 </t>
   </si>
   <si>
-    <t>Administrative Gender Addition</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the administrative gender of a person (Patient, Practitioner, ...). 
-The extension is used to add the missing codes and is applied in case the code for administrative gender itself is set to 'other'.</t>
+    <t>Additional administrative gender (Geschlecht)</t>
+  </si>
+  <si>
+    <t>Additional administrative gender code (Geschlecht) required in Austria that is not covered by the FHIR administrative gender codes. The extension is only applied in case the administrative gender itself is set to 'other' (Ergänzung zu 'other').</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -3884,10 +3901,10 @@
         <v>146</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>147</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>148</v>
+        <v>226</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
@@ -3969,7 +3986,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>156</v>
@@ -4081,7 +4098,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>162</v>
@@ -4195,7 +4212,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>167</v>
@@ -4311,7 +4328,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>177</v>
@@ -4377,10 +4394,10 @@
         <v>183</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4427,7 +4444,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>187</v>
@@ -4456,7 +4473,7 @@
         <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>189</v>
@@ -4472,10 +4489,10 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>21</v>
+        <v>235</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>192</v>
@@ -4543,7 +4560,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>197</v>
@@ -4572,7 +4589,7 @@
         <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>199</v>
@@ -4657,7 +4674,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>206</v>
@@ -4769,7 +4786,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>214</v>
@@ -4883,10 +4900,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4995,10 +5012,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5109,10 +5126,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5138,13 +5155,13 @@
         <v>157</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5194,7 +5211,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5203,7 +5220,7 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
@@ -5223,10 +5240,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5252,13 +5269,13 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5287,10 +5304,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5308,7 +5325,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5337,10 +5354,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5366,13 +5383,13 @@
         <v>146</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5422,7 +5439,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5440,7 +5457,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5451,10 +5468,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5480,13 +5497,13 @@
         <v>157</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5494,10 +5511,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -5536,7 +5553,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5565,13 +5582,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
@@ -5596,10 +5613,10 @@
         <v>146</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>147</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>148</v>
+        <v>276</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -5681,7 +5698,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>156</v>
@@ -5793,7 +5810,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>162</v>
@@ -5907,7 +5924,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>167</v>
@@ -6023,7 +6040,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>177</v>
@@ -6089,10 +6106,10 @@
         <v>183</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6139,7 +6156,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>187</v>
@@ -6168,7 +6185,7 @@
         <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>189</v>
@@ -6184,10 +6201,10 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>192</v>
@@ -6255,7 +6272,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>197</v>
@@ -6369,7 +6386,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>206</v>
@@ -6481,7 +6498,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>214</v>
@@ -6595,10 +6612,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6707,10 +6724,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6821,10 +6838,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6850,13 +6867,13 @@
         <v>157</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6906,7 +6923,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6915,7 +6932,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -6935,10 +6952,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6964,13 +6981,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6999,10 +7016,10 @@
         <v>183</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7020,7 +7037,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7049,10 +7066,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7078,13 +7095,13 @@
         <v>146</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7134,7 +7151,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7152,7 +7169,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7163,10 +7180,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7192,13 +7209,13 @@
         <v>157</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7206,10 +7223,10 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>21</v>
+        <v>293</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>21</v>
@@ -7248,7 +7265,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7277,13 +7294,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
@@ -7308,10 +7325,10 @@
         <v>146</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>147</v>
+        <v>296</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>148</v>
+        <v>297</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
@@ -7393,7 +7410,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>156</v>
@@ -7505,7 +7522,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>162</v>
@@ -7619,7 +7636,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>167</v>
@@ -7735,7 +7752,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>177</v>
@@ -7801,10 +7818,10 @@
         <v>183</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7851,7 +7868,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>187</v>
@@ -7880,7 +7897,7 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>189</v>
@@ -7918,7 +7935,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -7965,7 +7982,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>197</v>
@@ -8079,7 +8096,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>206</v>
@@ -8191,7 +8208,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>214</v>
@@ -8305,10 +8322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8331,70 +8348,70 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q59" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="R59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8412,21 +8429,21 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8449,19 +8466,19 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8510,7 +8527,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8525,13 +8542,13 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -8539,10 +8556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8565,19 +8582,19 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8626,7 +8643,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8641,13 +8658,13 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -8655,10 +8672,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8681,19 +8698,19 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -8742,7 +8759,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8754,16 +8771,16 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -8771,10 +8788,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8800,14 +8817,14 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -8835,10 +8852,10 @@
         <v>172</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -8856,7 +8873,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8871,13 +8888,13 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -8885,10 +8902,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8914,10 +8931,10 @@
         <v>157</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8997,10 +9014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9026,10 +9043,10 @@
         <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9107,13 +9124,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
@@ -9135,13 +9152,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9201,7 +9218,7 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>139</v>
@@ -9221,10 +9238,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9250,10 +9267,10 @@
         <v>157</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9304,7 +9321,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9333,10 +9350,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9359,17 +9376,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9418,7 +9435,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9433,13 +9450,13 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9447,10 +9464,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9473,17 +9490,17 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9532,7 +9549,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9550,10 +9567,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9561,10 +9578,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9587,13 +9604,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9644,7 +9661,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9659,13 +9676,13 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -9673,10 +9690,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9785,10 +9802,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9899,14 +9916,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -9928,10 +9945,10 @@
         <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>137</v>
@@ -9986,7 +10003,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10015,10 +10032,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10044,14 +10061,14 @@
         <v>146</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10100,7 +10117,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10118,7 +10135,7 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
@@ -10129,10 +10146,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10158,10 +10175,10 @@
         <v>178</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10188,13 +10205,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10212,7 +10229,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>88</v>
@@ -10230,10 +10247,10 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10241,10 +10258,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10270,14 +10287,14 @@
         <v>207</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10326,7 +10343,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10344,10 +10361,10 @@
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10355,10 +10372,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10384,10 +10401,10 @@
         <v>215</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10438,7 +10455,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10456,7 +10473,7 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
@@ -10467,10 +10484,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10496,16 +10513,16 @@
         <v>178</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10554,7 +10571,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10569,13 +10586,13 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
